--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/9905-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/9905-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2418FC4B-97F3-4FCC-B3E1-94F35FB662AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{33B09592-E595-429F-ACCB-E11A877EC717}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{3C8F2D1D-417D-4308-9332-67F2CF35BC78}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{D5BB7750-9AD1-4384-BD34-0FDF301E48A4}"/>
   </bookViews>
   <sheets>
     <sheet name="9905-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1589,24 +1589,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C00C3979-DE35-4709-8726-D3AAA1C5825D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D54F9A1B-0969-4305-8A84-09F98BA95A06}">
   <dimension ref="A1:X48"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="11.375" customWidth="1"/>
-    <col min="3" max="3" width="10.25" customWidth="1"/>
-    <col min="4" max="13" width="6.25" customWidth="1"/>
-    <col min="14" max="15" width="6.625" customWidth="1"/>
-    <col min="16" max="18" width="6.25" customWidth="1"/>
-    <col min="19" max="19" width="6.625" customWidth="1"/>
-    <col min="20" max="20" width="6.25" customWidth="1"/>
-    <col min="21" max="21" width="6.625" customWidth="1"/>
-    <col min="22" max="22" width="6.25" customWidth="1"/>
-    <col min="23" max="23" width="6.625" customWidth="1"/>
-    <col min="24" max="24" width="8.5" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1640,7 +1639,7 @@
       <c r="W1" s="31"/>
       <c r="X1" s="23"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
@@ -1676,7 +1675,7 @@
       <c r="W2" s="33"/>
       <c r="X2" s="34"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -1728,7 +1727,7 @@
       </c>
       <c r="X3" s="37"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="7"/>
@@ -1796,7 +1795,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="38">
         <v>2024</v>
       </c>
@@ -1868,7 +1867,7 @@
         <v>6.06</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="40">
         <v>2023</v>
       </c>
@@ -1940,7 +1939,7 @@
         <v>4.8899999999999997</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="38">
         <v>2022</v>
       </c>
@@ -2012,7 +2011,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="40">
         <v>2021</v>
       </c>
@@ -2084,7 +2083,7 @@
         <v>6.29</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="38">
         <v>2020</v>
       </c>
@@ -2156,7 +2155,7 @@
         <v>6.88</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="40">
         <v>2019</v>
       </c>
@@ -2228,7 +2227,7 @@
         <v>5.83</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="38">
         <v>2018</v>
       </c>
@@ -2300,7 +2299,7 @@
         <v>4.26</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="40">
         <v>2017</v>
       </c>
@@ -2372,7 +2371,7 @@
         <v>7.08</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="38">
         <v>2016</v>
       </c>
@@ -2444,7 +2443,7 @@
         <v>6.28</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="40">
         <v>2015</v>
       </c>
@@ -2516,7 +2515,7 @@
         <v>6.79</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="38">
         <v>2014</v>
       </c>
@@ -2588,7 +2587,7 @@
         <v>8.16</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="40">
         <v>2013</v>
       </c>
@@ -2660,7 +2659,7 @@
         <v>7.33</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="38">
         <v>2012</v>
       </c>
@@ -2732,7 +2731,7 @@
         <v>6.25</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="40">
         <v>2011</v>
       </c>
@@ -2804,7 +2803,7 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="38">
         <v>2010</v>
       </c>
@@ -2876,7 +2875,7 @@
         <v>5.51</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="40">
         <v>2009</v>
       </c>
@@ -2948,7 +2947,7 @@
         <v>5.35</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="38">
         <v>2008</v>
       </c>
@@ -3020,7 +3019,7 @@
         <v>7.66</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="40">
         <v>2007</v>
       </c>
@@ -3092,7 +3091,7 @@
         <v>9.85</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="38">
         <v>2006</v>
       </c>
@@ -3164,7 +3163,7 @@
         <v>7.19</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="40">
         <v>2005</v>
       </c>
@@ -3236,7 +3235,7 @@
         <v>7.66</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="38">
         <v>2004</v>
       </c>
@@ -3308,7 +3307,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="40">
         <v>2003</v>
       </c>
@@ -3380,7 +3379,7 @@
         <v>8.82</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="38">
         <v>2002</v>
       </c>
@@ -3452,7 +3451,7 @@
         <v>7.22</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="40">
         <v>2001</v>
       </c>
@@ -3524,7 +3523,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="38">
         <v>2000</v>
       </c>
@@ -3596,7 +3595,7 @@
         <v>14.7</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="40">
         <v>1999</v>
       </c>
@@ -3668,7 +3667,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="38">
         <v>1998</v>
       </c>
@@ -3740,7 +3739,7 @@
         <v>9.09</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="42">
         <v>1997</v>
       </c>
@@ -3812,7 +3811,7 @@
         <v>6.85</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="44"/>
       <c r="B33" s="45"/>
       <c r="C33" s="19" t="s">
@@ -3840,7 +3839,7 @@
       <c r="W33" s="51"/>
       <c r="X33" s="47"/>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="38">
         <v>1996</v>
       </c>
@@ -3912,7 +3911,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="40">
         <v>1995</v>
       </c>
@@ -3984,7 +3983,7 @@
         <v>5.36</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="38">
         <v>1994</v>
       </c>
@@ -4056,7 +4055,7 @@
         <v>9.51</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="42">
         <v>1993</v>
       </c>
@@ -4128,7 +4127,7 @@
         <v>5.66</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="44"/>
       <c r="B38" s="45"/>
       <c r="C38" s="19" t="s">
@@ -4156,7 +4155,7 @@
       <c r="W38" s="51"/>
       <c r="X38" s="47"/>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="38">
         <v>1992</v>
       </c>
@@ -4228,7 +4227,7 @@
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="40">
         <v>1991</v>
       </c>
@@ -4300,7 +4299,7 @@
         <v>4.87</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="52">
         <v>1990</v>
       </c>
@@ -4372,7 +4371,7 @@
         <v>9.0500000000000007</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="54"/>
       <c r="B42" s="55"/>
       <c r="C42" s="21" t="s">
@@ -4400,7 +4399,7 @@
       <c r="W42" s="61"/>
       <c r="X42" s="57"/>
     </row>
-    <row r="43" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="40">
         <v>1989</v>
       </c>
@@ -4472,7 +4471,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="38">
         <v>1988</v>
       </c>
@@ -4544,7 +4543,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="40">
         <v>1987</v>
       </c>
@@ -4616,7 +4615,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="38">
         <v>1986</v>
       </c>
@@ -4688,7 +4687,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="40">
         <v>1984</v>
       </c>
@@ -4760,7 +4759,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="38" t="s">
         <v>64</v>
       </c>
